--- a/寵物生活與健康管理/petproject/rag/data/faq_data.xlsx
+++ b/寵物生活與健康管理/petproject/rag/data/faq_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\114404ntub\寵物生活與健康管理\petproject\rag\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4732D4-B2C2-442F-A6EA-08D99585EFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF029628-12C2-4736-9AD4-4C65A47731A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="9970" firstSheet="30" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="26" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
